--- a/data/memories/memory_01/locales/es/documents/finance/Budget Draft.xlsx
+++ b/data/memories/memory_01/locales/es/documents/finance/Budget Draft.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Budget Draft</t>
+          <t>Proyecto de presupuesto</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,43 +469,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finance Department</t>
+          <t>Departamento de Finanzas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Budget Overview</t>
+          <t>Resumen del presupuesto</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimado</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Diferencia</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Office Operations</t>
+          <t>Operaciones de oficina</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Staffing</t>
+          <t>Dotación de personal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Archive Project</t>
+          <t>Proyecto de archivo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -593,21 +593,21 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Archive-related costs exceeded the initial estimate due to additional classification work and the discovery of undocumented material requiring review.</t>
+          <t>Los costos relacionados con los archivos excedieron la estimación inicial debido al trabajo de clasificación adicional y al descubrimiento de material indocumentado que requería revisión.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>This draft remains pending approval and should not be distributed outside Finance.</t>
+          <t>Este borrador permanece pendiente de aprobación y no debe distribuirse fuera de Finanzas.</t>
         </is>
       </c>
     </row>
